--- a/競爭對手追蹤模板.xlsx
+++ b/競爭對手追蹤模板.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1109,6 +1109,475 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>副牌促銷</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>第2支75折（最後週末）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026/03/20</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026/03/29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>買眼鏡或墨鏡第2支75折（週末限定）</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>第2支75折</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>週末衝業績，3/29截止，本週影響有限</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>🟡 中</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>監控週末業績變化</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69bbd0d86594a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EC促銷</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EC春季新品賞</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026/03/16</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>指定熱銷品88折、春季新品9折、配鏡滿$3800折$200</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>88折/9折/滿$3800折$200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>EC限定，鏡片折扣力道強，OD套餐整體CP仍優</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69b79ee18887f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ESG/行銷</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>廢鏡新思計畫</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026/03/01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026/05/31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>回收任何品牌舊眼鏡+追蹤IG送$300折價券</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>送$300折價券</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>全通路</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ESG+獲客策略，回收競品轉換客戶，長期影響大</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>評估類似回收計畫可行性</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://www.jins.com/tw/news/news-69b125db355d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6周年慶（最後3天）</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026/03/02</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026/03/29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>滿$6,000折$666</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>~11% off</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>OD低門檻策略更有優勢；3/29截止後觀察流量</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>觀察活動結束後客流變化</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://meganeichiba.com.tw/news/170</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>廣三SOGO/Lalaport南港 一週年祭</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>滿$3,000折$400、滿$6,000折$800</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>滿$3K折$400</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>折扣力道高，台中/台北競爭注意</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>注意台中/南港門市客流</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://meganeichiba.com.tw/news/171</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>滿$5,500現折$500（即將截止）</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026/03/01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>全門市單筆滿$5,500現折$500</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>~9% off</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Klassic定位中高端，客群與OD重疊度低</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>門市促銷</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>niceynook 單件9折</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026/03/01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>副牌niceynook指定門市單件9折</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>9折</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>門市</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>副牌促銷，影響有限</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>🟢 低</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1682,6 +2151,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>疑似關閉</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>未確認門市（-1）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>待確認</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.klassicglobal.com/pages/stores</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Klassic本週抓取確認16間，較前次17間少1，持續追蹤</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1694,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1961,6 +2477,118 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OWNDAYS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>78</v>
+      </c>
+      <c r="D10" t="n">
+        <v>78</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>全台78間，本週無異動</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jins</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
+        <v>94</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>本週抓取90間；上週記錄94間（含RIM口徑差異，下週確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>眼鏡市場</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>維持35間，南紡開幕已計入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/03/26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Klassic</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Klassic本週抓取確認16間，較上次17間減少1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1972,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2694,38 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>南部市場競爭加劇（Jins台南MITSUI+眼鏡市場南紡同期開店）、Jins ESG回收活動為獲客新策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026/03/24-03/30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1. Klassic門市確認-1(16間) 2. 多促銷3/29-3/31集中截止 3. Jins門市計數差異待確認</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>⚠️ 中</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>把握競品促銷結束空窗(3/30起)，評估4月新活動；追蹤台南市場業績；確認Jins RIM計數口徑</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2759,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026/03/25</t>
+          <t>2026/03/26</t>
         </is>
       </c>
     </row>
@@ -2145,16 +2805,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -2277,7 +2937,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>7</v>
@@ -2286,7 +2946,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
